--- a/exports/trend_1d/COROMANDEL_full_report.xlsx
+++ b/exports/trend_1d/COROMANDEL_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q63"/>
+  <dimension ref="A1:U63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>6.05</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42037</v>
+        <v>42038</v>
       </c>
       <c r="H2" t="n">
-        <v>282.95</v>
+        <v>270.7</v>
       </c>
       <c r="I2" t="n">
         <v>282.8758212</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K2" t="n">
-        <v>-4.28</v>
+        <v>-8.42</v>
       </c>
       <c r="L2" t="n">
-        <v>5.51</v>
+        <v>9.51</v>
       </c>
       <c r="M2" t="n">
         <v>1.5</v>
       </c>
       <c r="N2" t="n">
-        <v>2.39</v>
+        <v>4.33</v>
       </c>
       <c r="O2" t="n">
         <v>-0.43</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>14.07</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42181</v>
+        <v>42184</v>
       </c>
       <c r="H3" t="n">
-        <v>246.55</v>
+        <v>254.6</v>
       </c>
       <c r="I3" t="n">
         <v>251.254238792722</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="K3" t="n">
-        <v>8.92</v>
+        <v>5.95</v>
       </c>
       <c r="L3" t="n">
         <v>11.71</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>98</v>
+        <v>99</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>6</v>
+      </c>
+      <c r="U3" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>14.21</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42212</v>
+        <v>42213</v>
       </c>
       <c r="H4" t="n">
-        <v>235.35</v>
+        <v>228.55</v>
       </c>
       <c r="I4" t="n">
         <v>230.2224491888927</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K4" t="n">
-        <v>-7.56</v>
+        <v>-10.23</v>
       </c>
       <c r="L4" t="n">
-        <v>8.35</v>
+        <v>10.9</v>
       </c>
       <c r="M4" t="n">
         <v>3.45</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>10.34</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42286</v>
+        <v>42289</v>
       </c>
       <c r="H5" t="n">
-        <v>165.75</v>
+        <v>185.15</v>
       </c>
       <c r="I5" t="n">
         <v>171.7855882518749</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K5" t="n">
-        <v>27.48</v>
+        <v>18.99</v>
       </c>
       <c r="L5" t="n">
         <v>10.15</v>
@@ -726,7 +785,7 @@
         <v>4.86</v>
       </c>
       <c r="N5" t="n">
-        <v>3.45</v>
+        <v>11.7</v>
       </c>
       <c r="O5" t="n">
         <v>-2.89</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>15.96</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42380</v>
+        <v>42381</v>
       </c>
       <c r="H6" t="n">
-        <v>178.95</v>
+        <v>175.95</v>
       </c>
       <c r="I6" t="n">
         <v>176.8826329458379</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K6" t="n">
-        <v>-3.35</v>
+        <v>-4.97</v>
       </c>
       <c r="L6" t="n">
         <v>9.48</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>11.71</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42450</v>
+        <v>42451</v>
       </c>
       <c r="H7" t="n">
-        <v>178.3</v>
+        <v>184.2</v>
       </c>
       <c r="I7" t="n">
         <v>183.1039019575264</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.34</v>
+        <v>-4.69</v>
       </c>
       <c r="L7" t="n">
-        <v>4.4</v>
+        <v>6.82</v>
       </c>
       <c r="M7" t="n">
         <v>2.52</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>10.22</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42555</v>
+        <v>42556</v>
       </c>
       <c r="H8" t="n">
-        <v>250.2</v>
+        <v>220.75</v>
       </c>
       <c r="I8" t="n">
         <v>233.9993707309171</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K8" t="n">
-        <v>35.83</v>
+        <v>19.84</v>
       </c>
       <c r="L8" t="n">
         <v>3.39</v>
@@ -897,7 +992,7 @@
         <v>4.36</v>
       </c>
       <c r="N8" t="n">
-        <v>6.34</v>
+        <v>11.77</v>
       </c>
       <c r="O8" t="n">
         <v>3.31</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U8" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>23.22</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42594</v>
+        <v>42598</v>
       </c>
       <c r="H9" t="n">
-        <v>257.75</v>
+        <v>263.75</v>
       </c>
       <c r="I9" t="n">
         <v>263.4047584355998</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K9" t="n">
-        <v>-16.76</v>
+        <v>-19.48</v>
       </c>
       <c r="L9" t="n">
         <v>20.88</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42579</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>12.76</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42636</v>
+        <v>42639</v>
       </c>
       <c r="H10" t="n">
-        <v>246.05</v>
+        <v>244.6</v>
       </c>
       <c r="I10" t="n">
         <v>245.7166527657533</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K10" t="n">
-        <v>-6.71</v>
+        <v>-7.26</v>
       </c>
       <c r="L10" t="n">
-        <v>7.47</v>
+        <v>7.68</v>
       </c>
       <c r="M10" t="n">
         <v>2.04</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42607</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>12.64</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42649</v>
+        <v>42650</v>
       </c>
       <c r="H11" t="n">
-        <v>257.65</v>
+        <v>269.85</v>
       </c>
       <c r="I11" t="n">
         <v>268.0683928301542</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K11" t="n">
-        <v>-5.34</v>
+        <v>-10.32</v>
       </c>
       <c r="L11" t="n">
-        <v>8.34</v>
+        <v>11.77</v>
       </c>
       <c r="M11" t="n">
         <v>1.22</v>
       </c>
       <c r="N11" t="n">
-        <v>3.15</v>
+        <v>4.74</v>
       </c>
       <c r="O11" t="n">
         <v>-0.59</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>12.89</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42684</v>
+        <v>42685</v>
       </c>
       <c r="H12" t="n">
-        <v>257.4</v>
+        <v>248.3</v>
       </c>
       <c r="I12" t="n">
         <v>252.7936507715219</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K12" t="n">
-        <v>-4.61</v>
+        <v>-7.99</v>
       </c>
       <c r="L12" t="n">
         <v>14.77</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>20.41</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42712</v>
+        <v>42713</v>
       </c>
       <c r="H13" t="n">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="I13" t="n">
         <v>279.0976541321873</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K13" t="n">
-        <v>-8.74</v>
+        <v>-14.38</v>
       </c>
       <c r="L13" t="n">
-        <v>9.539999999999999</v>
+        <v>14.74</v>
       </c>
       <c r="M13" t="n">
         <v>2.59</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>14.24</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42803</v>
+        <v>42804</v>
       </c>
       <c r="H14" t="n">
-        <v>319.05</v>
+        <v>315.9</v>
       </c>
       <c r="I14" t="n">
         <v>317.4967126263402</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K14" t="n">
-        <v>12.34</v>
+        <v>11.23</v>
       </c>
       <c r="L14" t="n">
         <v>5.9</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>10.64</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42836</v>
+        <v>42837</v>
       </c>
       <c r="H15" t="n">
-        <v>336.6</v>
+        <v>344.55</v>
       </c>
       <c r="I15" t="n">
         <v>340.7459224166369</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K15" t="n">
-        <v>-6.55</v>
+        <v>-9.07</v>
       </c>
       <c r="L15" t="n">
-        <v>7.58</v>
+        <v>9.73</v>
       </c>
       <c r="M15" t="n">
         <v>2.44</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42824</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>10.58</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42956</v>
+        <v>42957</v>
       </c>
       <c r="H16" t="n">
-        <v>423.55</v>
+        <v>400.5</v>
       </c>
       <c r="I16" t="n">
         <v>416.6401995000614</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K16" t="n">
-        <v>22.93</v>
+        <v>16.24</v>
       </c>
       <c r="L16" t="n">
         <v>4.66</v>
@@ -1353,7 +1544,7 @@
         <v>1.62</v>
       </c>
       <c r="N16" t="n">
-        <v>3.5</v>
+        <v>5.44</v>
       </c>
       <c r="O16" t="n">
         <v>2.36</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42852</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>5</v>
+      </c>
+      <c r="U16" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>15.76</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43013</v>
+        <v>43014</v>
       </c>
       <c r="H17" t="n">
-        <v>458.9</v>
+        <v>459.7</v>
       </c>
       <c r="I17" t="n">
         <v>459.3504557353502</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K17" t="n">
-        <v>-14.58</v>
+        <v>-14.78</v>
       </c>
       <c r="L17" t="n">
-        <v>14.86</v>
+        <v>18.6</v>
       </c>
       <c r="M17" t="n">
         <v>2.03</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>8.640000000000001</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43147</v>
+        <v>43150</v>
       </c>
       <c r="H18" t="n">
-        <v>525.15</v>
+        <v>516.9</v>
       </c>
       <c r="I18" t="n">
         <v>521.3432002487596</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="K18" t="n">
-        <v>14.24</v>
+        <v>12.44</v>
       </c>
       <c r="L18" t="n">
         <v>1.63</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>5</v>
+      </c>
+      <c r="U18" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>12.65</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43284</v>
+        <v>43285</v>
       </c>
       <c r="H19" t="n">
-        <v>423.55</v>
+        <v>434.5</v>
       </c>
       <c r="I19" t="n">
         <v>434.2362365482729</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K19" t="n">
-        <v>18.06</v>
+        <v>15.94</v>
       </c>
       <c r="L19" t="n">
         <v>12.01</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>93</v>
+        <v>94</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>6</v>
+      </c>
+      <c r="U19" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>12.01</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43299</v>
+        <v>43300</v>
       </c>
       <c r="H20" t="n">
-        <v>393.15</v>
+        <v>390.5</v>
       </c>
       <c r="I20" t="n">
         <v>390.6515552006781</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K20" t="n">
-        <v>-9.52</v>
+        <v>-10.13</v>
       </c>
       <c r="L20" t="n">
-        <v>10.23</v>
+        <v>11.28</v>
       </c>
       <c r="M20" t="n">
         <v>1.05</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>11.4</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43319</v>
+        <v>43320</v>
       </c>
       <c r="H21" t="n">
-        <v>426.15</v>
+        <v>436.6</v>
       </c>
       <c r="I21" t="n">
         <v>433.0951542663302</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K21" t="n">
-        <v>-9.130000000000001</v>
+        <v>-11.81</v>
       </c>
       <c r="L21" t="n">
         <v>14.21</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>12.14</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43371</v>
+        <v>43374</v>
       </c>
       <c r="H22" t="n">
-        <v>403.95</v>
+        <v>393.65</v>
       </c>
       <c r="I22" t="n">
         <v>394.0448390783203</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K22" t="n">
-        <v>-7.48</v>
+        <v>-9.84</v>
       </c>
       <c r="L22" t="n">
-        <v>11.25</v>
+        <v>11.35</v>
       </c>
       <c r="M22" t="n">
         <v>1.22</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>12.27</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43403</v>
+        <v>43404</v>
       </c>
       <c r="H23" t="n">
-        <v>413.7</v>
+        <v>421.4</v>
       </c>
       <c r="I23" t="n">
         <v>415.5970033004418</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K23" t="n">
-        <v>-5.09</v>
+        <v>-7.05</v>
       </c>
       <c r="L23" t="n">
-        <v>6.4</v>
+        <v>7.96</v>
       </c>
       <c r="M23" t="n">
         <v>1.44</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43398</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>14.21</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43558</v>
+        <v>43559</v>
       </c>
       <c r="H24" t="n">
-        <v>470.6</v>
+        <v>455.1</v>
       </c>
       <c r="I24" t="n">
         <v>459.1180373495603</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K24" t="n">
-        <v>11.68</v>
+        <v>8</v>
       </c>
       <c r="L24" t="n">
         <v>6.72</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>105</v>
+        <v>106</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>6</v>
+      </c>
+      <c r="U24" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>13.48</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43612</v>
+        <v>43613</v>
       </c>
       <c r="H25" t="n">
-        <v>422.1</v>
+        <v>434.85</v>
       </c>
       <c r="I25" t="n">
         <v>432.8249303078008</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K25" t="n">
-        <v>7.25</v>
+        <v>4.45</v>
       </c>
       <c r="L25" t="n">
         <v>3.98</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43580</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>9.960000000000001</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43655</v>
+        <v>43656</v>
       </c>
       <c r="H26" t="n">
-        <v>401.9</v>
+        <v>392.55</v>
       </c>
       <c r="I26" t="n">
         <v>399.8212334387292</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K26" t="n">
-        <v>-7.58</v>
+        <v>-9.73</v>
       </c>
       <c r="L26" t="n">
-        <v>8.09</v>
+        <v>10.54</v>
       </c>
       <c r="M26" t="n">
         <v>0.8100000000000001</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>10.04</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43719</v>
+        <v>43720</v>
       </c>
       <c r="H27" t="n">
-        <v>379.85</v>
+        <v>397.95</v>
       </c>
       <c r="I27" t="n">
         <v>390.647552710585</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K27" t="n">
-        <v>3.24</v>
+        <v>-1.38</v>
       </c>
       <c r="L27" t="n">
         <v>3.22</v>
@@ -1980,7 +2303,7 @@
         <v>1.31</v>
       </c>
       <c r="N27" t="n">
-        <v>3.6</v>
+        <v>4.77</v>
       </c>
       <c r="O27" t="n">
         <v>-2.33</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>11.8</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43901</v>
+        <v>43902</v>
       </c>
       <c r="H28" t="n">
-        <v>622.1</v>
+        <v>576.55</v>
       </c>
       <c r="I28" t="n">
         <v>578.4978866525317</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K28" t="n">
-        <v>56.33</v>
+        <v>44.88</v>
       </c>
       <c r="L28" t="n">
         <v>4.86</v>
       </c>
       <c r="M28" t="n">
-        <v>2.64</v>
+        <v>2.98</v>
       </c>
       <c r="N28" t="n">
-        <v>2.55</v>
+        <v>7.32</v>
       </c>
       <c r="O28" t="n">
         <v>4.77</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>124</v>
+        <v>125</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>7</v>
+      </c>
+      <c r="U28" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>15.05</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43972</v>
+        <v>43973</v>
       </c>
       <c r="H29" t="n">
-        <v>615</v>
+        <v>650.55</v>
       </c>
       <c r="I29" t="n">
         <v>644.5577473641737</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K29" t="n">
-        <v>-6.67</v>
+        <v>-12.83</v>
       </c>
       <c r="L29" t="n">
-        <v>9.789999999999999</v>
+        <v>14.14</v>
       </c>
       <c r="M29" t="n">
         <v>3.07</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>15.5</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>44057</v>
+        <v>44060</v>
       </c>
       <c r="H30" t="n">
-        <v>752.1</v>
+        <v>728.25</v>
       </c>
       <c r="I30" t="n">
         <v>736.0545896795866</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="K30" t="n">
-        <v>15.61</v>
+        <v>11.94</v>
       </c>
       <c r="L30" t="n">
         <v>6.08</v>
@@ -2151,7 +2510,7 @@
         <v>3.15</v>
       </c>
       <c r="N30" t="n">
-        <v>2.75</v>
+        <v>3.17</v>
       </c>
       <c r="O30" t="n">
         <v>5.78</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43979</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>4</v>
+      </c>
+      <c r="U30" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>13.05</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>44088</v>
+        <v>44089</v>
       </c>
       <c r="H31" t="n">
-        <v>790.4</v>
+        <v>807.55</v>
       </c>
       <c r="I31" t="n">
         <v>801.755856052278</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K31" t="n">
-        <v>-8.529999999999999</v>
+        <v>-10.89</v>
       </c>
       <c r="L31" t="n">
         <v>13.97</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>44070</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,22 +2627,22 @@
         <v>14.03</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44113</v>
+        <v>44116</v>
       </c>
       <c r="H32" t="n">
-        <v>723.4</v>
+        <v>711.8</v>
       </c>
       <c r="I32" t="n">
         <v>714.0425511537214</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K32" t="n">
-        <v>-10.42</v>
+        <v>-11.86</v>
       </c>
       <c r="L32" t="n">
-        <v>11.39</v>
+        <v>12.02</v>
       </c>
       <c r="M32" t="n">
         <v>2.15</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>14.44</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44149</v>
+        <v>44152</v>
       </c>
       <c r="H33" t="n">
-        <v>748.25</v>
+        <v>789.55</v>
       </c>
       <c r="I33" t="n">
         <v>778.7192537641655</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K33" t="n">
-        <v>-5.12</v>
+        <v>-10.92</v>
       </c>
       <c r="L33" t="n">
-        <v>8.01</v>
+        <v>11.41</v>
       </c>
       <c r="M33" t="n">
         <v>1.51</v>
       </c>
       <c r="N33" t="n">
-        <v>3.12</v>
+        <v>5.52</v>
       </c>
       <c r="O33" t="n">
         <v>-1.6</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>13.14</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44229</v>
+        <v>44230</v>
       </c>
       <c r="H34" t="n">
-        <v>789.4</v>
+        <v>784.65</v>
       </c>
       <c r="I34" t="n">
         <v>786.8752372344983</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.02</v>
+        <v>-0.62</v>
       </c>
       <c r="L34" t="n">
         <v>5.46</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>4</v>
+      </c>
+      <c r="U34" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>11.42</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44335</v>
+        <v>44336</v>
       </c>
       <c r="H35" t="n">
-        <v>775.3</v>
+        <v>806</v>
       </c>
       <c r="I35" t="n">
         <v>782.3099171842683</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K35" t="n">
-        <v>1.19</v>
+        <v>-2.72</v>
       </c>
       <c r="L35" t="n">
-        <v>1.66</v>
+        <v>4.51</v>
       </c>
       <c r="M35" t="n">
-        <v>1.6</v>
+        <v>3.96</v>
       </c>
       <c r="N35" t="n">
-        <v>3.36</v>
+        <v>3.96</v>
       </c>
       <c r="O35" t="n">
         <v>-0.6</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>4</v>
+      </c>
+      <c r="U35" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>7.94</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44417</v>
+        <v>44418</v>
       </c>
       <c r="H36" t="n">
-        <v>851.3</v>
+        <v>827.15</v>
       </c>
       <c r="I36" t="n">
         <v>828.2460251881248</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K36" t="n">
-        <v>5.62</v>
+        <v>2.62</v>
       </c>
       <c r="L36" t="n">
         <v>2.47</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>4</v>
+      </c>
+      <c r="U36" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>13.36</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44474</v>
+        <v>44475</v>
       </c>
       <c r="H37" t="n">
-        <v>827.05</v>
+        <v>857</v>
       </c>
       <c r="I37" t="n">
         <v>851.7288417835574</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K37" t="n">
-        <v>0.01</v>
+        <v>-3.61</v>
       </c>
       <c r="L37" t="n">
-        <v>4.45</v>
+        <v>4.58</v>
       </c>
       <c r="M37" t="n">
         <v>0.96</v>
       </c>
       <c r="N37" t="n">
-        <v>3.27</v>
+        <v>3.62</v>
       </c>
       <c r="O37" t="n">
         <v>-2.84</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>9.82</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44497</v>
+        <v>44498</v>
       </c>
       <c r="H38" t="n">
-        <v>796.9</v>
+        <v>785.6</v>
       </c>
       <c r="I38" t="n">
         <v>788.9718173010604</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K38" t="n">
-        <v>-7.01</v>
+        <v>-8.33</v>
       </c>
       <c r="L38" t="n">
         <v>9.68</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>9.93</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44566</v>
+        <v>44567</v>
       </c>
       <c r="H39" t="n">
-        <v>773.9</v>
+        <v>777.15</v>
       </c>
       <c r="I39" t="n">
         <v>774.8113253571667</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K39" t="n">
-        <v>1.49</v>
+        <v>1.08</v>
       </c>
       <c r="L39" t="n">
         <v>3.21</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>6.38</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44615</v>
+        <v>44616</v>
       </c>
       <c r="H40" t="n">
-        <v>790.85</v>
+        <v>733.85</v>
       </c>
       <c r="I40" t="n">
         <v>745.0525839042359</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K40" t="n">
-        <v>1.76</v>
+        <v>-5.57</v>
       </c>
       <c r="L40" t="n">
-        <v>5.92</v>
+        <v>6.12</v>
       </c>
       <c r="M40" t="n">
-        <v>2.52</v>
+        <v>5</v>
       </c>
       <c r="N40" t="n">
-        <v>3.6</v>
+        <v>7.21</v>
       </c>
       <c r="O40" t="n">
         <v>0.42</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>14.21</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44636</v>
+        <v>44637</v>
       </c>
       <c r="H41" t="n">
-        <v>799.8</v>
+        <v>849.45</v>
       </c>
       <c r="I41" t="n">
         <v>838.1630845625599</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K41" t="n">
-        <v>-8.99</v>
+        <v>-15.75</v>
       </c>
       <c r="L41" t="n">
-        <v>9.25</v>
+        <v>16.61</v>
       </c>
       <c r="M41" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="N41" t="n">
-        <v>3.37</v>
+        <v>6.21</v>
       </c>
       <c r="O41" t="n">
         <v>-7.21</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>12.37</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44827</v>
+        <v>44830</v>
       </c>
       <c r="H42" t="n">
-        <v>1008.4</v>
+        <v>969.55</v>
       </c>
       <c r="I42" t="n">
         <v>990.6968908955597</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K42" t="n">
-        <v>18.71</v>
+        <v>14.14</v>
       </c>
       <c r="L42" t="n">
         <v>8.16</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>130</v>
+        <v>131</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>7</v>
+      </c>
+      <c r="U42" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>11.81</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44902</v>
+        <v>44903</v>
       </c>
       <c r="H43" t="n">
-        <v>918.15</v>
+        <v>966.25</v>
       </c>
       <c r="I43" t="n">
         <v>966.1051830989971</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K43" t="n">
-        <v>5.3</v>
+        <v>0.34</v>
       </c>
       <c r="L43" t="n">
         <v>5.8</v>
@@ -2892,7 +3407,7 @@
         <v>1.94</v>
       </c>
       <c r="N43" t="n">
-        <v>2.12</v>
+        <v>5.24</v>
       </c>
       <c r="O43" t="n">
         <v>-3.85</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>4</v>
+      </c>
+      <c r="U43" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>9.25</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44916</v>
+        <v>44917</v>
       </c>
       <c r="H44" t="n">
-        <v>913.15</v>
+        <v>892.05</v>
       </c>
       <c r="I44" t="n">
         <v>894.3103600498065</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K44" t="n">
-        <v>-5.5</v>
+        <v>-7.68</v>
       </c>
       <c r="L44" t="n">
-        <v>6.26</v>
+        <v>8.67</v>
       </c>
       <c r="M44" t="n">
         <v>0.16</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>9.6</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44964</v>
+        <v>44965</v>
       </c>
       <c r="H45" t="n">
-        <v>901.15</v>
+        <v>918.25</v>
       </c>
       <c r="I45" t="n">
         <v>902.0458320065734</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K45" t="n">
-        <v>-1.02</v>
+        <v>-2.94</v>
       </c>
       <c r="L45" t="n">
-        <v>3.1</v>
+        <v>3.46</v>
       </c>
       <c r="M45" t="n">
         <v>1.06</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,22 +3593,22 @@
         <v>8.4</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44999</v>
+        <v>45000</v>
       </c>
       <c r="H46" t="n">
-        <v>881.3</v>
+        <v>872.7</v>
       </c>
       <c r="I46" t="n">
         <v>873.1766872333529</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K46" t="n">
-        <v>-4.02</v>
+        <v>-4.96</v>
       </c>
       <c r="L46" t="n">
-        <v>5.16</v>
+        <v>5.79</v>
       </c>
       <c r="M46" t="n">
         <v>0.62</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>7.86</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45021</v>
+        <v>45022</v>
       </c>
       <c r="H47" t="n">
-        <v>897.95</v>
+        <v>923.05</v>
       </c>
       <c r="I47" t="n">
         <v>917.4556485546044</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K47" t="n">
-        <v>-2.89</v>
+        <v>-5.77</v>
       </c>
       <c r="L47" t="n">
-        <v>3.12</v>
+        <v>5.99</v>
       </c>
       <c r="M47" t="n">
         <v>0.73</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>8.84</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45224</v>
+        <v>45225</v>
       </c>
       <c r="H48" t="n">
-        <v>1118.15</v>
+        <v>1073.4</v>
       </c>
       <c r="I48" t="n">
         <v>1093.510793227739</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K48" t="n">
-        <v>21.14</v>
+        <v>16.29</v>
       </c>
       <c r="L48" t="n">
         <v>3.45</v>
@@ -3177,7 +3752,7 @@
         <v>4.57</v>
       </c>
       <c r="N48" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="O48" t="n">
         <v>2.8</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>137</v>
+        <v>138</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>7</v>
+      </c>
+      <c r="U48" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>9.26</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="H49" t="n">
-        <v>1124.25</v>
+        <v>1140.55</v>
       </c>
       <c r="I49" t="n">
         <v>1136.678157691006</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K49" t="n">
-        <v>-4.74</v>
+        <v>-6.26</v>
       </c>
       <c r="L49" t="n">
         <v>6.48</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>6.78</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45299</v>
+        <v>45300</v>
       </c>
       <c r="H50" t="n">
-        <v>1200.4</v>
+        <v>1170.6</v>
       </c>
       <c r="I50" t="n">
         <v>1175.27799709964</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K50" t="n">
-        <v>5.25</v>
+        <v>2.63</v>
       </c>
       <c r="L50" t="n">
         <v>2.1</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>10.35</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45384</v>
+        <v>45385</v>
       </c>
       <c r="H51" t="n">
-        <v>1133.3</v>
+        <v>1144.8</v>
       </c>
       <c r="I51" t="n">
         <v>1137.077310601761</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K51" t="n">
-        <v>3.19</v>
+        <v>2.2</v>
       </c>
       <c r="L51" t="n">
         <v>4.15</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>4</v>
+      </c>
+      <c r="U51" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>8.390000000000001</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45568</v>
+        <v>45569</v>
       </c>
       <c r="H52" t="n">
-        <v>1669.3</v>
+        <v>1619.9</v>
       </c>
       <c r="I52" t="n">
         <v>1624.635080416217</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K52" t="n">
-        <v>45.82</v>
+        <v>41.5</v>
       </c>
       <c r="L52" t="n">
         <v>6.37</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>125</v>
+        <v>126</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>7</v>
+      </c>
+      <c r="U52" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>11.23</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45602</v>
+        <v>45603</v>
       </c>
       <c r="H53" t="n">
-        <v>1726.1</v>
+        <v>1777.95</v>
       </c>
       <c r="I53" t="n">
         <v>1726.198895760468</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K53" t="n">
-        <v>-6.56</v>
+        <v>-9.76</v>
       </c>
       <c r="L53" t="n">
-        <v>6.97</v>
+        <v>11.06</v>
       </c>
       <c r="M53" t="n">
         <v>1.23</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>10.09</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45667</v>
+        <v>45670</v>
       </c>
       <c r="H54" t="n">
-        <v>1922.45</v>
+        <v>1808</v>
       </c>
       <c r="I54" t="n">
         <v>1815.408097981259</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K54" t="n">
-        <v>8.130000000000001</v>
+        <v>1.69</v>
       </c>
       <c r="L54" t="n">
         <v>6.34</v>
@@ -3519,7 +4166,7 @@
         <v>1.41</v>
       </c>
       <c r="N54" t="n">
-        <v>2.63</v>
+        <v>5.95</v>
       </c>
       <c r="O54" t="n">
         <v>3</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>11.37</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45729</v>
+        <v>45733</v>
       </c>
       <c r="H55" t="n">
-        <v>1797.7</v>
+        <v>1888.85</v>
       </c>
       <c r="I55" t="n">
         <v>1857.092370074242</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="K55" t="n">
-        <v>0.57</v>
+        <v>-4.47</v>
       </c>
       <c r="L55" t="n">
         <v>5.96</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>14.5</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45881</v>
+        <v>45882</v>
       </c>
       <c r="H56" t="n">
-        <v>2397.2</v>
+        <v>2257.7</v>
       </c>
       <c r="I56" t="n">
         <v>2379.075533482387</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K56" t="n">
-        <v>26.91</v>
+        <v>19.53</v>
       </c>
       <c r="L56" t="n">
         <v>5.78</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>102</v>
+        <v>103</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>6</v>
+      </c>
+      <c r="U56" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>15.13</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45987</v>
+        <v>45988</v>
       </c>
       <c r="H57" t="n">
-        <v>2298</v>
+        <v>2366.7</v>
       </c>
       <c r="I57" t="n">
         <v>2336.163257517238</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K57" t="n">
-        <v>-1.79</v>
+        <v>-4.83</v>
       </c>
       <c r="L57" t="n">
         <v>10.73</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>5</v>
+      </c>
+      <c r="U57" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="58">
@@ -3726,25 +4421,25 @@
         <v>8.69</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="H58" t="n">
-        <v>2220</v>
+        <v>2179.8</v>
       </c>
       <c r="I58" t="n">
         <v>2194.893297750773</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="K58" t="n">
-        <v>-6.2</v>
+        <v>-7.9</v>
       </c>
       <c r="L58" t="n">
-        <v>8.119999999999999</v>
+        <v>8.48</v>
       </c>
       <c r="M58" t="n">
-        <v>0.95</v>
+        <v>1.8</v>
       </c>
       <c r="N58" t="n">
         <v>5.39</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>4</v>
+      </c>
+      <c r="U58" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>9.18</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="H59" t="n">
-        <v>2010.9</v>
+        <v>2116</v>
       </c>
       <c r="I59" t="n">
         <v>2108.057354416894</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K59" t="n">
-        <v>7.75</v>
+        <v>2.93</v>
       </c>
       <c r="L59" t="n">
         <v>1.11</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>14.52</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="H60" t="n">
-        <v>1927.6</v>
+        <v>1866.2</v>
       </c>
       <c r="I60" t="n">
         <v>1894.504779117727</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K60" t="n">
-        <v>-8.9</v>
+        <v>-11.81</v>
       </c>
       <c r="L60" t="n">
-        <v>10.12</v>
+        <v>12.17</v>
       </c>
       <c r="M60" t="n">
         <v>2.65</v>
       </c>
       <c r="N60" t="n">
-        <v>2.84</v>
+        <v>3.19</v>
       </c>
       <c r="O60" t="n">
         <v>5.23</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>11.78</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="H61" t="n">
-        <v>1916.7</v>
+        <v>1986.3</v>
       </c>
       <c r="I61" t="n">
         <v>1941.137016882751</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K61" t="n">
-        <v>-2.71</v>
+        <v>-6.44</v>
       </c>
       <c r="L61" t="n">
-        <v>3.55</v>
+        <v>7.12</v>
       </c>
       <c r="M61" t="n">
         <v>1.13</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>11.67</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="H62" t="n">
-        <v>1996.1</v>
+        <v>1926.6</v>
       </c>
       <c r="I62" t="n">
         <v>1966.098378503766</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K62" t="n">
-        <v>0.49</v>
+        <v>-3.01</v>
       </c>
       <c r="L62" t="n">
         <v>4.33</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>3</v>
+      </c>
+      <c r="U62" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -4035,6 +4790,14 @@
       <c r="Q63" t="n">
         <v>45</v>
       </c>
+      <c r="R63" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8993,7 +9756,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>67.90000000000001</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="6">
@@ -9003,7 +9766,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7">
@@ -9013,7 +9776,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="8">
@@ -9023,7 +9786,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
@@ -9033,7 +9796,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10">
@@ -9043,7 +9806,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11">
@@ -9053,7 +9816,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
@@ -9063,7 +9826,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13">
@@ -9073,7 +9836,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>23</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="14">
@@ -9083,7 +9846,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.91</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="15">
@@ -9093,7 +9856,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6.76</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="16">
@@ -9103,7 +9866,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-1.07</v>
+        <v>-4.61</v>
       </c>
     </row>
     <row r="17">
@@ -9113,7 +9876,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>56.33</v>
+        <v>44.88</v>
       </c>
     </row>
     <row r="18">
@@ -9123,7 +9886,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>45.9</v>
+        <v>36.1</v>
       </c>
     </row>
     <row r="19">
@@ -9133,7 +9896,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7.18</v>
+        <v>8.23</v>
       </c>
     </row>
     <row r="20">
@@ -9143,7 +9906,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6.37</v>
+        <v>7.12</v>
       </c>
     </row>
     <row r="21">
@@ -9163,7 +9926,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23">
@@ -9173,7 +9936,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24">
@@ -9183,7 +9946,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.17</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="25">
@@ -9203,7 +9966,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.16</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="27">
@@ -9213,7 +9976,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>9.56</v>
+        <v>11.77</v>
       </c>
     </row>
     <row r="28">
@@ -9223,7 +9986,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29">
